--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Global Stable Equity Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Global Stable Equity Fund (FOF).xlsx
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Global Stable Equity Fund (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -89,7 +89,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -913,10 +913,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>11693.35</v>
+        <v>10182.71</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9967378571094</v>
+        <v>0.9953211978342</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -941,13 +941,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="14">
-        <v>311162.296</v>
+        <v>267879.866</v>
       </c>
       <c r="F7" s="15">
-        <v>11693.35</v>
+        <v>10182.71</v>
       </c>
       <c r="G7" s="16">
-        <v>0.9967378571094</v>
+        <v>0.9953211978342</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -978,10 +978,10 @@
         <v>12</v>
       </c>
       <c r="F9" s="9">
-        <v>47.08</v>
+        <v>60.04</v>
       </c>
       <c r="G9" s="10">
-        <v>0.0040130859259</v>
+        <v>0.0058686817868</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>12</v>
@@ -1012,10 +1012,10 @@
         <v>12</v>
       </c>
       <c r="F11" s="18">
-        <v>-8.809778500000903</v>
+        <v>-12.173154899999645</v>
       </c>
       <c r="G11" s="19">
-        <v>-0.0007509430354603219</v>
+        <v>-0.0011898796210919479</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>12</v>
@@ -1038,10 +1038,10 @@
         <v>12</v>
       </c>
       <c r="F12" s="18">
-        <v>11731.6202215</v>
+        <v>10230.5768451</v>
       </c>
       <c r="G12" s="19">
-        <v>0.9999999999998397</v>
+        <v>0.9999999999999081</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>12</v>
